--- a/docs/build-provenance/PROMPT_MASTER_LOG.xlsx
+++ b/docs/build-provenance/PROMPT_MASTER_LOG.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster Index" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prompt Chain'!$A$1:$S$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prompt Chain'!$A$1:$S$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S95"/>
+  <dimension ref="A1:S106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9018,8 +9018,1009 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>0095</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>TRC-FW1-5-reflect-0095</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-23T17:05:00Z</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>FW1.5</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>reflect</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>the framework v1.4 reflection + the hardening review that mechanically exposed 'unwired realness' as E14</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>framework-v1.5-reflection</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>framework</t>
+        </is>
+      </c>
+      <c r="M96" s="5" t="inlineStr">
+        <is>
+          <t>Owner-requested tree-of-thought reflection on how to further harden the framework so iterations are truly optimized, after the 10-lens adversarial hardening review of I0-&gt;I11. Orchestrator-authored v1.5: E14 wired-path/integration gate (import-graph reachability ratchet), E15 seam mock&lt;-&gt;production parity gate, lens-completeness doctrine (derive lens set from NFR+regulatory surface), two-tier done (Definition of Ready + Production-Readiness gate), program spine (interface-freeze across iterations), critical-finding protocol (N-skeptic + mutation-tested regression + red-team re-attack).</t>
+        </is>
+      </c>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>the 10-lens hardening review's 162 findings (dominant theme: 'unwired realness' - production-shaped modules reached only by tests); framework v1.4 baseline</t>
+        </is>
+      </c>
+      <c r="O96" s="5" t="inlineStr">
+        <is>
+          <t>framework docs v1.5 (SKILL/personas/enforcement-kit/operating-model); E14 tooling BUILT + DOGFOODED (check-wiring.mjs found 134 unwired lib modules; ratchet passes at baseline, fails on a new orphan) + wiring-baseline.json; repackaged skill + framework_bundle.tgz + agentic-build-framework-v1.5.zip (README updated)</t>
+        </is>
+      </c>
+      <c r="P96" s="5" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q96" s="5" t="inlineStr"/>
+      <c r="R96" s="5" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S96" s="5" t="inlineStr">
+        <is>
+          <t>Tree-of-thought used in the reflection itself: enumerated candidate hardenings (more personas vs mechanical gates vs process doctrine), scored against blast-radius/reversibility/dogfoolability, pruned to the set that is mechanically enforceable now. E14 is dependency-free and proven against the real repo (134 orphans found), not prose. E15/lens-completeness/program-spine/critical-finding are doctrine+DoD until their first hardening iteration exercises them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>0096</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>TRC-12-HW0-0096</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T17:25:00Z</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>HW0</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>framework v1.5 (E14/E15 + program spine + two-tier done) applied to the first hardening iteration</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>I12-HW0-demo-preservation</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>hardening/safety-net</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW0 safety net BEFORE any wiring: build the demo-preservation golden-snapshot harness + gate (constraint #2), the E15 seam mock&lt;-&gt;production parity registry, the installer frontend-only+mock lock (constraint #3), and the program spine (I12-I21 dependency graph + interface registry + phase gates). External measures preserved as authored mock (constraint #4).</t>
+        </is>
+      </c>
+      <c r="N97" s="6" t="inlineStr">
+        <is>
+          <t>HARDENING_PLAN.md HW0; dataMode seam registry; authored demo surfaces (wholePersonGraphData, smartFhirMockData, mockData, describeDataModes)</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/demoPreservation/{fingerprint,capture,shape,parity,index}.ts + tests/demoPreservation/{demo-preservation,seam-parity}.test.ts + goldens; docs/framework/{PROGRAM_SPINE,INSTALL_PROFILES}.md; package.json check:demo; check-wiring.mjs harness exemption. Gates: tsc 0, 26 tests pass (deterministic x2), E14 134/134, mock-default lock green.</t>
+        </is>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q97" s="6" t="inlineStr"/>
+      <c r="R97" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S97" s="6" t="inlineStr">
+        <is>
+          <t>Freezes contract C-DEMO for the whole program. Volatile demo timestamps normalized so the golden regenerates byte-identically. demoPreservation is a CI gate harness -&gt; a first-class E14 exemption, not unwired production. Production-readiness = the gate is real+deterministic+CI-wired; it now guards HW1-HW6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>TRC-13-HW-SEC-0097</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T17:40:00Z</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>HW-SEC</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>HW0 demo-preservation gate; the pre-existing Principal member-scope model (tenant dimension added ABOVE org scope)</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>I13-HWSEC-tenant-boundary</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>hardening/security</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5, DoR-&gt;DoD] Publish the tenant/plan/LOB boundary (program-spine keystone C-TEN) and enforce it: even an org-scoped reviewer is bounded to their tenant/LOB. Close the documented BOLA on clinical FHIR reads. Seam-gated (tenancy): mock=single demo tenant (demo intact), production=per-record tenant + IdP-claim actor scope, fail-closed. Lens set: security(owning)+domain-fidelity+stub-legitimacy+negative-space.</t>
+        </is>
+      </c>
+      <c r="N98" s="6" t="inlineStr">
+        <is>
+          <t>security.md (20 findings, 2 Crit: no tenant/LOB isolation, BOLA clinical reads); existing Principal/MemberScope model; dataMode seam registry; patient payer/contract fields</t>
+        </is>
+      </c>
+      <c r="O98" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/security/tenant/{types,resolve,authz,index}.ts; FHIR route BOLA gate wired (canAccessMemberTenantAware); tenancy seam in dataMode+seamDispositions(real-impl)+governance prober; tests/security/tenant.test.ts. Gates: tsc 0, 34 tests pass, E14 134/134 (WIRED reachable 535-&gt;539), demo golden diff = +tenancy only (demo preserved), FHIR route tests 7 pass.</t>
+        </is>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q98" s="6" t="inlineStr"/>
+      <c r="R98" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S98" s="6" t="inlineStr">
+        <is>
+          <t>Freezes C-TEN for HW1/HW2/HW3/HW-FIN/HW4 (stores built tenant-scoped, no retrofit). Genuinely wired (E14 reachable +4), not unit-tested-only. Production fails closed on absent claim (safe). Residual HW-SEC items (secrets rotation, rate-limit, CSP/CSRF, SBOM, IAL2) are follow-on; live IdP claim emission is the NS-05 ceiling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>0098</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>TRC-14-HW1-0098</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T17:55:00Z</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>HW1</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>HW0 gate + HW-SEC C-TEN; wires the pre-existing-but-orphaned projector+outbox (the exact defect E14 was built to catch)</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>I14-HW1-projection-consumer</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>hardening/reliability</t>
+        </is>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW1 core: close REC-01 (the #1 'unwired realness' finding) - wire the outbox-&gt;projector consumer to a REAL entry point with a resumable per-member checkpoint, idempotent, per-member FIFO. Seam-gated store resolution (mock in-memory vs production durable/fail-closed). Freezes C-STORE consumer half. Right-sized (L12) to the dominant finding; remaining HW1 breadth scheduled.</t>
+        </is>
+      </c>
+      <c r="N99" s="6" t="inlineStr">
+        <is>
+          <t>reconciliation.md REC-01/03; ha-scale.md HS-02; existing outbox (store/envelope/sequencing) + graph projector (project/projectEvent) that were unit-tested but uncalled from any real path</t>
+        </is>
+      </c>
+      <c r="O99" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/graph/consumer/{projectionConsumer,checkpoint,provider,index}.ts + src/app/api/ops/projection/run/route.ts (ops-authz, audited) + tests/graph/projectionConsumer.test.ts. Gates: tsc 0, 3 tests pass, E14 134/134 with entries 225-&gt;226 + reachable 539-&gt;544 (WIRED, proven not test-only), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P99" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q99" s="6" t="inlineStr"/>
+      <c r="R99" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S99" s="6" t="inlineStr">
+        <is>
+          <t>REC-01 was THE canonical 'unwired realness' example in the hardening plan; E14 now proves it wired (reachable +5). Production checkpoint/outbox/graph factories are fail-closed hooks (NS-05 live-infra ceiling). Remaining HW1 (store migration, scheduler, circuit-breakers, readiness=liveness, migration-lock, observability, DR) is scheduled follow-on; demo untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>TRC-15-HW2-0099</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T18:10:00Z</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>HW2</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>HW1 (audit hangs off request + projection paths); the existing PHI-safe audit event shape</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>I15-HW2-tamper-evident-audit</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>hardening/audit</t>
+        </is>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW2 core: make the audit trail tamper-evident (AUD-01) - a SHA-256 hash-chain over the PHI-safe events, verifiable + break-locating, in-memory demo default + fail-closed durable factory; wire it into audit() and an ops verify route; fix real actor identity (AUD-02) replacing hardcoded 'session-user'. Freezes C-AUD. Right-sized to the compliance blocker.</t>
+        </is>
+      </c>
+      <c r="N100" s="6" t="inlineStr">
+        <is>
+          <t>audit.md (AUD-01 tamper-evidence, AUD-02 actor identity); existing JSONL audit sink; evidence-ledger immutability pattern</t>
+        </is>
+      </c>
+      <c r="O100" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/server/auditLedger.ts (hash-chain + verifyChain + fail-closed factory) + audit() integration + src/app/api/ops/audit/verify/route.ts (ops/auditor authz) + AUD-02 fix in FHIR route (4 actors) + tests/server/auditLedger.test.ts. Gates: tsc 0, 4 ledger tests + 35 audit-suite pass, E14 134/134 (entries 226-&gt;227, reachable 544-&gt;546 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q100" s="6" t="inlineStr"/>
+      <c r="R100" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S100" s="6" t="inlineStr">
+        <is>
+          <t>Tamper-evidence is production-real (node:crypto SHA-256 chain, detection+location tested). Durable pg ledger (append-only + immutability trigger) is the NS-05 live-infra step. Remaining HW2 breadth (Part2/break-glass persistence, before-after on all mutations, accounting-of-disclosures/RADV-OCR export, retention) scheduled. Demo untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>TRC-16-HW-AI-0100</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>HW-AI</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>HW2 audit (decisions recorded to the tamper-evident spine); the existing agent autonomy-tier model (invariant added ABOVE it)</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>I16-HWAI-decision-invariant</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>hardening/ai-governance</t>
+        </is>
+      </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW-AI core (3-Crit finding): a TIER-INDEPENDENT invariant at the propose/decide seam - no adverse coverage-affecting action (denial/termination/reduction) auto-resolves under HITL/HOTL/autonomous; resolves ONLY on a qualified human decision with complete provenance (fired rule+version+member-facing reason+appeal). Kills the HOTL SLA-timeout auto-approve + autonomous-tier flip. Wire into the runtime auto-approve branch + a real decision route. Freezes C-DEC.</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="inlineStr">
+        <is>
+          <t>ai-governance.md (16 findings, 3 Crit: SLA-timeout auto-approve, autonomy-tier flip on coverage, no decision provenance); agentRuntime engine auto-approve path; AutonomyTier HITL/HOTL/autonomous</t>
+        </is>
+      </c>
+      <c r="O101" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/agents/governance/{decisionGate,decisionProvenance,index}.ts + engine.ts auto-approve gated on isAutoApprovable + src/app/api/pa/decision/route.ts (reviewer authz, invariant enforced: 403 no-human, 422 incomplete-provenance) + tests. Gates: tsc 0, 6 governance + 54 agent/runtime tests pass, E14 orphans 134-&gt;130 (ratchet SHRANK: route wired governance + 4 agentRuntime modules; baseline re-frozen 130), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q101" s="6" t="inlineStr"/>
+      <c r="R101" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S101" s="6" t="inlineStr">
+        <is>
+          <t>PHASE 1 (safe-to-pilot) CLOSE: HW0+HW-SEC+HW1core+HW2core+HW-AI. The invariant is genuinely wired (E14 ratchet shrank 4) - the decision route pulled orphaned agentRuntime modules into a real path. Favorable auto-approvals unaffected (54 runtime tests green) - demo preserved. Remaining HW-AI breadth (eval gate, fairness/disparate-impact monitoring, model/prompt versioning+drift) scheduled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>TRC-17-HW3-0101</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T18:55:00Z</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>HW3</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>HW1 C-STORE (corrections re-project through the consumer); HW2 audit; HW-SEC tenant scope on writes</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>I17-HW3-record-lifecycle</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>hardening/reprocessing</t>
+        </is>
+      </c>
+      <c r="M102" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW3 core: content-hash record lifecycle (RP-01) - a true resend dedupes but a CORRECTION (same key, changed content) RE-projects; entered-in-error voids/retracts, never hard-delete (CRUD-02). Tenant-scoped + audited CRUD route (PUT correction / DELETE void). Freezes C-LIFE for HW-FIN + HW4.</t>
+        </is>
+      </c>
+      <c r="N102" s="6" t="inlineStr">
+        <is>
+          <t>crud.md/reprocessing.md (RP-01 correction-reprojection, CRUD-02 void); existing key-only idempotency store (drops corrections); lifecycle purge/right-to-delete infra</t>
+        </is>
+      </c>
+      <c r="O102" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/lifecycle/recordLifecycle.ts (content-hash classify: new/unchanged/correction/void/revoid + fail-closed store) + src/app/api/records/[type]/[id]/route.ts (PUT/DELETE, tenant+audit) + lifecycle index exports + tests. Gates: tsc 0, 6 tests pass, E14 orphans 130-&gt;122 (ratchet SHRANK 8: CRUD route wired recordLifecycle + purge/right-to-delete/legal-hold/policy/audit; baseline re-frozen 122; reachable 554-&gt;564), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P102" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q102" s="6" t="inlineStr"/>
+      <c r="R102" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S102" s="6" t="inlineStr">
+        <is>
+          <t>RP-01 keystone: content-hash idempotency is the fix for the key-only store silently dropping corrections. Genuinely wired - the CRUD route pulled 8 orphaned lifecycle modules into a real path (backlog 134-&gt;122 across the program). Remaining HW3 breadth (consent CRUD, care-plan versioning, EMPI merge/unmerge, raw-payload retention, bitemporal projection, replay wiring, 834 recon) scheduled. Demo untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>0102</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>TRC-18-HW-FIN-0102</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>HW-FIN</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>HW3 C-LIFE (retract = a void lifecycle); HW-SEC tenant scope; HW2 audit</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>I18-HWFIN-radv-integrity</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>hardening/financial-integrity</t>
+        </is>
+      </c>
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW-FIN core (6-Crit lens): make every captured HCC RADV-defensible - require MEAT (monitored/evaluated/assessed/treated) + source-document linkage + valid F2F DOS + provider NPI; a pre-submission SCRUB withholds anything non-defensible; an unsupported diagnosis can be RETRACTED before submission (ties to C-LIFE void). Freezes C-SUB submission gate.</t>
+        </is>
+      </c>
+      <c r="N103" s="6" t="inlineStr">
+        <is>
+          <t>financial-integrity.md (6 Crit: no MEAT/source linkage=every HCC a RADV takeback, no encounter-submission pipeline, unsupported HCC cannot be retracted pre-submission); existing HCC classifier + encounter mapping</t>
+        </is>
+      </c>
+      <c r="O103" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/finance/riskAdjustment/{meat,submission,index}.ts (assessRadvDefensibility + evaluateSubmission + retractDiagnosis + scrubForSubmission) + src/app/api/risk-adjustment/hcc/route.ts (POST scrub / DELETE retract, tenant+audit) + tests. Gates: tsc 0, 5 tests pass, E14 122/122 (reachable 564-&gt;568 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q103" s="6" t="inlineStr"/>
+      <c r="R103" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S103" s="6" t="inlineStr">
+        <is>
+          <t>PHASE 2 CLOSE (HW3+HW-FIN). Addresses the highest-severity financial Crit: no diagnosis earns risk revenue unless it survives a RADV audit, and an unsupported one is retracted BEFORE submission (not clawed back after). Remaining HW-FIN breadth (full EDPS/RAPS submission + 999/277CA/MAO-002 recon + resubmission, COB, FWA/overpayment, TCOC/PMPM/MLR from adjudicated dollars) scheduled. Demo untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>0103</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>TRC-19-HW4-0103</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T19:45:00Z</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>HW4</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>HW0 golden (pins the authored gaps); HW2 audit; HW-SEC authz. The governance gate self-corrected the graph/wpcRecord classification.</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>I19-HW4-deqm-measures</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>hardening/whole-person-care</t>
+        </is>
+      </c>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5, constraint #4] HW4 core: external HEDIS/Stars/MIPS measures are INGESTED not computed - a Da Vinci DEQM MeasureReport ingestion adapter behind a `measures` seam. mock=today's authored demo gaps (preserved EXACTLY), production=external feed (fail-closed). Normalized MeasureGap; E15 parity between dispositions. Freezes C-MEAS.</t>
+        </is>
+      </c>
+      <c r="N104" s="6" t="inlineStr">
+        <is>
+          <t>HW4 constraint (measures external, ingested to FHIR Measure/MeasureReport/Gaps, demo preserved at all costs); authored mockHEDIS/STARS/MIPS arrays; DEQM population semantics</t>
+        </is>
+      </c>
+      <c r="O104" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/measures/{types,deqmIngest,mockMeasures,index}.ts + measures seam (dataMode+seamDispositions fail-closed-stub+prober) + RECLASSIFIED graph+wpcRecord mock-only-&gt;fail-closed-stub (governance gate caught HW1/HW3 added real consumers; probers added) + src/app/api/measures/gaps/route.ts + tests. Gates: tsc 0, 7 measures + 12 governance tests pass, E14 122/122 (reachable 568-&gt;573 WIRED), demo golden = +measures seam only, authored measure panels BYTE-IDENTICAL.</t>
+        </is>
+      </c>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q104" s="6" t="inlineStr"/>
+      <c r="R104" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S104" s="6" t="inlineStr">
+        <is>
+          <t>Constraint #4 honored mechanically: mock reproduces the authored HEDIS/STARS/MIPS gaps byte-identically (read-only normalization), production ingests DEQM and derives gap=denom-numer (never computes the measure). The E14+governance gates BOTH did their job - E14 proved wiring, governance forced the honest graph/wpcRecord reclassification. Remaining HW4 breadth (holistic-context seam, barrier/keystone analytics, living care plan, SDOH, agent orchestration) scheduled - each the same mock=demo/production=real seam. Demo untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>TRC-20-HW5-0104</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T20:30:00Z</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>HW5</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>every prior hardening module (now under mutation test); the E13 tool from framework v1.4 (bug found + fixed by dogfooding it)</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>I20-HW5-test-hardening</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>hardening/test-effectiveness</t>
+        </is>
+      </c>
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW5: expand E13 mutation to the hardening-critical modules (T-03) and prove real catch-power; NAME the non-code go-live gates. Dogfooding surfaced a real bug in check-mutation.mjs (|| as regex = zero-width match everywhere). Fixed the tool (regex-escape + string-mask + mut-equiv markers), then closed every REAL gap the fixed tool found by STRENGTHENING tests.</t>
+        </is>
+      </c>
+      <c r="N105" s="6" t="inlineStr">
+        <is>
+          <t>testing.md T-03 (mutation on critical set); the 6 new hardening modules + 3 original targets; the check-mutation.mjs regex bug</t>
+        </is>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>Fixed check-mutation.mjs (opRegex escape + maskNonCode + mut-equiv) + mutation-targets.json expanded to 9 modules + strengthened tests (decisionGate 75-&gt;100, auditLedger 83-&gt;100, recordLifecycle 67-&gt;100, meat 33-&gt;100, membership 67-&gt;100) + tests/terminology/membersForVersion.test.ts + 4 documented equivalent-mutant markers + docs/framework/GO_LIVE_GATES.md. Gates: tsc 0, E13 mutation PASSES all 9 targets, 50 tests pass, E14 122/122, demo 26.</t>
+        </is>
+      </c>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q105" s="6" t="inlineStr"/>
+      <c r="R105" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S105" s="6" t="inlineStr">
+        <is>
+          <t>The framework's own gate improved the framework: dogfooding E13 on the new modules exposed a zero-width-regex bug in check-mutation.mjs; fixing it then surfaced 5 real test gaps (all closed by strengthening tests, never deleting mutants) + 4 provably-equivalent mutants (documented). Every hardening-critical module now has PROVEN catch-power. Remaining HW5 breadth (contract/Inferno in CI, testcontainer concurrency, D4 load/soak, property/fuzz, chaos) needs live infra - named in GO_LIVE_GATES.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>0105</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>TRC-21-HW6-0105</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T20:50:00Z</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>HW6</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>HW-FIN risk-adjustment (the rollup extends the existing scrub surface)</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>I21-HW6-backlog-register</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>hardening/policy-fidelity</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW6 (non-blocker close): produce the E8 living-risk register for the 9 remaining policy-fidelity items (honest status/owner) rather than forcing a build of non-blockers; land the one self-contained READY item (HW6-2 ICD-10 category rollup) genuinely wired into the existing risk-adjustment route.</t>
+        </is>
+      </c>
+      <c r="N106" s="6" t="inlineStr">
+        <is>
+          <t>HARDENING_PLAN.md HW6 (terminology residuals, min-necessary Part 2, consent-revocation propagation, survivorship tiebreak - MED/policy-fidelity, not blockers)</t>
+        </is>
+      </c>
+      <c r="O106" s="6" t="inlineStr">
+        <is>
+          <t>docs/framework/HW6_BACKLOG_REGISTER.md (9 items, status+owner) + src/lib/finance/riskAdjustment/icdRollup.ts (icdCategory/rollupWithheldByCategory) wired into /api/risk-adjustment/hcc response + tests/finance/icdRollup.test.ts. Gates: tsc 0, 3 tests pass, E14 122/122 (reachable +1 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q106" s="6" t="inlineStr"/>
+      <c r="R106" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S106" s="6" t="inlineStr">
+        <is>
+          <t>PROGRAM CLOSE (I12-I21, 10 iterations, Phases 1-3). HW6 scoped honestly as non-blocker: the register (E8 discipline) schedules the content-gated items (NS-05 ceiling) and the bounded refinements; one ready item built + wired. Whole program: demo preserved at every step (golden changed only by additive seam entries), unwired-realness backlog burned down 134-&gt;122, provenance 105 rows E11-clean.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S95"/>
+  <autoFilter ref="A1:S106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9030,7 +10031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11605,6 +12606,303 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>0095</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>TRC-FW1-5-reflect-0095</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>BUILD IFW1.5</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>framework-v1.5-reflection</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>framework docs v1.5 (SKILL/personas/enforcement-kit/operating-model); E14 tooling BUILT + DOGFOODED (check-wiring.mjs found 134 unwired lib modules; ratchet passes at baseline, fails on a new orphan) + wiring-baseline.json; repackaged skill + framework_bundle.tgz + agentic-build-framework-v1.5.zip (README updated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>0096</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>TRC-12-HW0-0096</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I12</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>I12-HW0-demo-preservation</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/demoPreservation/{fingerprint,capture,shape,parity,index}.ts + tests/demoPreservation/{demo-preservation,seam-parity}.test.ts + goldens; docs/framework/{PROGRAM_SPINE,INSTALL_PROFILES}.md; package.json check:demo; check-wiring.mjs harness exemption. Gates: tsc 0, 26 tests pass (deterministic x2), E14 134/134, mock-default lock green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>TRC-13-HW-SEC-0097</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I13</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>I13-HWSEC-tenant-boundary</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/security/tenant/{types,resolve,authz,index}.ts; FHIR route BOLA gate wired (canAccessMemberTenantAware); tenancy seam in dataMode+seamDispositions(real-impl)+governance prober; tests/security/tenant.test.ts. Gates: tsc 0, 34 tests pass, E14 134/134 (WIRED reachable 535-&gt;539), demo golden diff = +tenancy only (demo preserved), FHIR route tests 7 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>0098</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>TRC-14-HW1-0098</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I14</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>I14-HW1-projection-consumer</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/graph/consumer/{projectionConsumer,checkpoint,provider,index}.ts + src/app/api/ops/projection/run/route.ts (ops-authz, audited) + tests/graph/projectionConsumer.test.ts. Gates: tsc 0, 3 tests pass, E14 134/134 with entries 225-&gt;226 + reachable 539-&gt;544 (WIRED, proven not test-only), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>0099</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>TRC-15-HW2-0099</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I15</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>I15-HW2-tamper-evident-audit</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/server/auditLedger.ts (hash-chain + verifyChain + fail-closed factory) + audit() integration + src/app/api/ops/audit/verify/route.ts (ops/auditor authz) + AUD-02 fix in FHIR route (4 actors) + tests/server/auditLedger.test.ts. Gates: tsc 0, 4 ledger tests + 35 audit-suite pass, E14 134/134 (entries 226-&gt;227, reachable 544-&gt;546 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>TRC-16-HW-AI-0100</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I16</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>I16-HWAI-decision-invariant</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/agents/governance/{decisionGate,decisionProvenance,index}.ts + engine.ts auto-approve gated on isAutoApprovable + src/app/api/pa/decision/route.ts (reviewer authz, invariant enforced: 403 no-human, 422 incomplete-provenance) + tests. Gates: tsc 0, 6 governance + 54 agent/runtime tests pass, E14 orphans 134-&gt;130 (ratchet SHRANK: route wired governance + 4 agentRuntime modules; baseline re-frozen 130), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>0101</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>TRC-17-HW3-0101</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I17</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>I17-HW3-record-lifecycle</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/lifecycle/recordLifecycle.ts (content-hash classify: new/unchanged/correction/void/revoid + fail-closed store) + src/app/api/records/[type]/[id]/route.ts (PUT/DELETE, tenant+audit) + lifecycle index exports + tests. Gates: tsc 0, 6 tests pass, E14 orphans 130-&gt;122 (ratchet SHRANK 8: CRUD route wired recordLifecycle + purge/right-to-delete/legal-hold/policy/audit; baseline re-frozen 122; reachable 554-&gt;564), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>0102</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>TRC-18-HW-FIN-0102</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I18</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>I18-HWFIN-radv-integrity</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/finance/riskAdjustment/{meat,submission,index}.ts (assessRadvDefensibility + evaluateSubmission + retractDiagnosis + scrubForSubmission) + src/app/api/risk-adjustment/hcc/route.ts (POST scrub / DELETE retract, tenant+audit) + tests. Gates: tsc 0, 5 tests pass, E14 122/122 (reachable 564-&gt;568 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>0103</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>TRC-19-HW4-0103</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I19</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>I19-HW4-deqm-measures</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/measures/{types,deqmIngest,mockMeasures,index}.ts + measures seam (dataMode+seamDispositions fail-closed-stub+prober) + RECLASSIFIED graph+wpcRecord mock-only-&gt;fail-closed-stub (governance gate caught HW1/HW3 added real consumers; probers added) + src/app/api/measures/gaps/route.ts + tests. Gates: tsc 0, 7 measures + 12 governance tests pass, E14 122/122 (reachable 568-&gt;573 WIRED), demo golden = +measures seam only, authored measure panels BYTE-IDENTICAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>TRC-20-HW5-0104</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I20</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>I20-HW5-test-hardening</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>Fixed check-mutation.mjs (opRegex escape + maskNonCode + mut-equiv) + mutation-targets.json expanded to 9 modules + strengthened tests (decisionGate 75-&gt;100, auditLedger 83-&gt;100, recordLifecycle 67-&gt;100, meat 33-&gt;100, membership 67-&gt;100) + tests/terminology/membersForVersion.test.ts + 4 documented equivalent-mutant markers + docs/framework/GO_LIVE_GATES.md. Gates: tsc 0, E13 mutation PASSES all 9 targets, 50 tests pass, E14 122/122, demo 26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>0105</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>TRC-21-HW6-0105</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I21</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>I21-HW6-backlog-register</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>docs/framework/HW6_BACKLOG_REGISTER.md (9 items, status+owner) + src/lib/finance/riskAdjustment/icdRollup.ts (icdCategory/rollupWithheldByCategory) wired into /api/risk-adjustment/hcc response + tests/finance/icdRollup.test.ts. Gates: tsc 0, 3 tests pass, E14 122/122 (reachable +1 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/build-provenance/PROMPT_MASTER_LOG.xlsx
+++ b/docs/build-provenance/PROMPT_MASTER_LOG.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster Index" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prompt Chain'!$A$1:$S$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Prompt Chain'!$A$1:$S$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S106"/>
+  <dimension ref="A1:S113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10019,8 +10019,645 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>TRC-22-HW1-B-0106</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T21:20:00Z</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>HW1-B</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>HW1 C-STORE (the projection drain is now a scheduled job under a breaker + observability)</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>I22-HW1B-reliability</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>hardening/reliability-breadth</t>
+        </is>
+      </c>
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW1 breadth: circuit-breaker + timeout for external seams (HS-03); deterministic scheduler for the outbox-&gt;projector drain + reconciliation (REC-03/HS-02, previously invoked by nothing); observability (metrics/latency/SLO); readiness=liveness (HS-06). Wired via /api/ops/health.</t>
+        </is>
+      </c>
+      <c r="N107" s="6" t="inlineStr">
+        <is>
+          <t>ha-scale.md HS-03/HS-06; reconciliation.md REC-03; the HW1 projection consumer (now driven by a real scheduled job)</t>
+        </is>
+      </c>
+      <c r="O107" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/reliability/{circuitBreaker,scheduler,bootstrap,index}.ts + src/lib/observability/{context,index}.ts + src/app/api/ops/health/route.ts (GET health+SLO, POST scheduler tick) + tests. Gates: tsc 0, 5 tests pass, E14 122/122 (entries 231-&gt;232, reachable 574-&gt;581 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q107" s="6" t="inlineStr"/>
+      <c r="R107" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S107" s="6" t="inlineStr">
+        <is>
+          <t>Closes HS-03 (breaker+timeout), REC-03/HS-02 (scheduled sweep), HS-06 (liveness), observability. Deterministic (clock injected) so unit-testable; production binds the same API to a real worker + metrics backend. Demo untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>TRC-23-HW2-B-0107</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T21:45:00Z</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>HW2-B</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>HW2 C-AUD (disclosure is the member-facing dimension of the audit spine); HW-SEC tenant scope</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>I23-HW2B-disclosures</t>
+        </is>
+      </c>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>hardening/compliance-breadth</t>
+        </is>
+      </c>
+      <c r="M108" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW2 breadth: HIPAA accounting-of-disclosures (AUD-10) - record who received a member's PHI, when, purpose; classify accountable vs exempt (treatment/payment/operations); enforce 6-year retention (flag purgeable, never auto-delete). Wired: FHIR break-glass records an accountable disclosure; /api/ops/disclosures returns the accounting.</t>
+        </is>
+      </c>
+      <c r="N108" s="6" t="inlineStr">
+        <is>
+          <t>audit.md AUD-10 (accounting-of-disclosures, read-audit, retention); the C-AUD tamper-evident ledger; the FHIR break-glass path</t>
+        </is>
+      </c>
+      <c r="O108" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/server/disclosure.ts (DisclosureLog + isAccountable + retention + fail-closed factory) + FHIR break-glass disclosure recording + src/app/api/ops/disclosures/route.ts (tenant+authz) + tests. Gates: tsc 0, disclosure+fhir tests pass, E14 122/122 (entries 232-&gt;233, reachable 581-&gt;583 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P108" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q108" s="6" t="inlineStr"/>
+      <c r="R108" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S108" s="6" t="inlineStr">
+        <is>
+          <t>AUD-10 accounting-of-disclosures with HIPAA accountable/exempt classification + 6-year retention. PHI-safe (references+purpose only). Break-glass over a consent opt-out is correctly recorded as accountable. Demo untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>0108</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>TRC-24-HW-FIN-B-0108</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T22:05:00Z</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>HW-FIN-B</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>HW-FIN C-SUB (the scrub feeds submittable encounters into this pipeline)</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>I24-HWFINB-submission</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>hardening/financial-breadth</t>
+        </is>
+      </c>
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW-FIN breadth: the encounter-submission pipeline (C-SUB pipeline half) - build a submission batch, reconcile against 999/277CA/MAO-002 acknowledgments (a reject at ANY level blocks acceptance), drive resubmission with attempt limits; COB order-of-benefits (MSP + Medicaid-last-resort + birthday rule). Only ACCEPTED encounters earn risk revenue.</t>
+        </is>
+      </c>
+      <c r="N109" s="6" t="inlineStr">
+        <is>
+          <t>financial-integrity.md (no encounter-submission pipeline = no risk revenue earned; COB order-of-benefits); HW-FIN C-SUB submission gate</t>
+        </is>
+      </c>
+      <c r="O109" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/finance/submission/{pipeline,cob,index}.ts (buildBatch/reconcile/buildResubmission + orderOfBenefits/primaryPayer) + src/app/api/finance/submission/route.ts (build + reconcile modes, tenant+authz) + tests. Gates: tsc 0, 6 tests pass, E14 122/122 (entries 233-&gt;234, reachable 583-&gt;587 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P109" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q109" s="6" t="inlineStr"/>
+      <c r="R109" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S109" s="6" t="inlineStr">
+        <is>
+          <t>Closes the 'no risk revenue earned' Crit: nothing is earned until an encounter is ACCEPTED (no rejecting ack at 999/277CA/MAO-002). COB prevents overpayment/FWA exposure. Live X12/EDPS transport is the NS-05 ceiling; the reconciliation logic is production-real. Demo untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>0109</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>TRC-25-HW-AI-B-0109</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T22:25:00Z</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>HW-AI-B</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>HW-AI C-DEC (fairness monitors the decisions the invariant governs)</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>I25-HWAIB-fairness</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>hardening/ai-governance-breadth</t>
+        </is>
+      </c>
+      <c r="M110" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW-AI breadth: fairness/disparate-impact monitoring (the equity claim, previously ZERO tested). EEOC four-fifths rule over AI-influenced decision outcomes by PHI-safe cohort; flag a cohort whose favorable rate &lt; 80% of the reference; report only, never auto-act. Wired: the PA decision route records the cohort outcome; /api/ops/fairness reports.</t>
+        </is>
+      </c>
+      <c r="N110" s="6" t="inlineStr">
+        <is>
+          <t>ai-governance.md (zero fairness/equity testing); HW-AI C-DEC decision surface</t>
+        </is>
+      </c>
+      <c r="O110" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/agents/governance/fairness.ts (aggregate + disparateImpact four-fifths + record/current) + decision-route cohort recording + src/app/api/ops/fairness/route.ts (409 when flagged) + tests. Gates: tsc 0, 4 tests pass, E14 122/122 (entries 234-&gt;235, reachable 587-&gt;589 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P110" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q110" s="6" t="inlineStr"/>
+      <c r="R110" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S110" s="6" t="inlineStr">
+        <is>
+          <t>Addresses the equity Crit with the EEOC four-fifths rule; small-sample cohorts reported but not flagged (no false alarm). PHI-safe (coarse cohort labels + counts). Reports for human review, never auto-acts on a disparity. Demo untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>TRC-26-HW4-B-0110</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T22:45:00Z</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>HW4-B</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>HW1 C-STORE graph + HW-SEC tenant scope; the existing authored holistic engine (mock disposition)</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>I26-HW4B-holistic-context</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>hardening/whole-person-breadth</t>
+        </is>
+      </c>
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW4 breadth: holistic-context SEAM (WPC-01/02) - the engine returned rich context only for authored demo members; the real projected graph reached no route. mock/seeded=authored engine context (demo intact, Maria et al.); production=aggregate the real projected graph via a registered aggregator, fail-closed. UI reads one interface; config chooses the source.</t>
+        </is>
+      </c>
+      <c r="N111" s="6" t="inlineStr">
+        <is>
+          <t>whole-person-care.md WPC-01/02 (empty context for non-demo members; projected graph wired to zero routes); existing holisticContextEngine.buildContext</t>
+        </is>
+      </c>
+      <c r="O111" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/wpc/holisticContext.ts (resolveHolisticContext seam + fail-closed aggregator) + src/app/api/wpc/context/route.ts (tenant+authz, 503 fail-closed) + tests. Gates: tsc 0, 3 tests pass, E14 122/122 (entries 235-&gt;236, reachable 589-&gt;591 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q111" s="6" t="inlineStr"/>
+      <c r="R111" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S111" s="6" t="inlineStr">
+        <is>
+          <t>De-hardcoding the demo = ADDING the production branch, never deleting the mock (constraint #2). The projected graph now reaches a real route via the seam. Production aggregator is the NS-05 wiring step; mock preserves the demo exactly. Demo untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>0111</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>TRC-27-HW5-B-0111</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-23T23:05:00Z</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>HW5-B</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>every hardening module (now property-tested for invariants, not just examples)</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>I27-HW5B-property-tests</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>hardening/test-breadth</t>
+        </is>
+      </c>
+      <c r="M112" s="6" t="inlineStr">
+        <is>
+          <t>[framework v1.5] HW5 breadth: property/fuzz tests (dependency-free seeded PRNG, reproducible) asserting INVARIANTS over all inputs for the hardening logic: contentHash order-independence+sensitivity, DEQM gapCount=max(0,denom-numer), tenant-scope membership, COB medicaid-never-primary, adverse-action monotonicity, record-lifecycle unchanged-vs-correction.</t>
+        </is>
+      </c>
+      <c r="N112" s="6" t="inlineStr">
+        <is>
+          <t>testing.md T-05 (property/fuzz); the hardening modules from I12-I26</t>
+        </is>
+      </c>
+      <c r="O112" s="6" t="inlineStr">
+        <is>
+          <t>tests/property/invariants.test.ts (6 properties x 300 randomized runs = 1800 assertions, seeded mulberry32). Gates: tsc 0, 6 property tests pass, demo 26 pass, E14 122/122 unchanged (test-only).</t>
+        </is>
+      </c>
+      <c r="P112" s="6" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q112" s="6" t="inlineStr"/>
+      <c r="R112" s="6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S112" s="6" t="inlineStr">
+        <is>
+          <t>Invariant-based testing complements the example-based unit tests + the E13 mutation gate: 1800 randomized assertions found no invariant violation. Deterministic seed so any future failure reproduces. Remaining HW5 breadth (contract/Inferno in CI, testcontainer concurrency, D4 load/soak, chaos) needs live infra - named in GO_LIVE_GATES.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>TRC-E13-FIX-fix-0112</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-24T00:10:00Z</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>E13-FIX</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>the E13 test-link tool from framework v1.4 (bug found from the owner's CI feedback, fixed same way as the E13 mutation-tool bug in HW5)</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>spine</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>E13-testlink-ratchet</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>framework/enforcement</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>Owner-reported: E13 test-coverage gate FAILS on every commit (273 modules need test linkage). Root cause: check-testlink.mjs ran WHOLE-REPO as a hard fail (a 200+ module pre-existing backlog can never pass), and matched only FILENAME stems - so a new module imported via a barrel (its symbols used, filename not) was a FALSE POSITIVE. Fix: make the check SYMBOL-AWARE (a test using any exported symbol links the module, following barrel re-exports) and a RATCHET (testlink-baseline.json freezes the backlog; only NEW untested modules fail), matching E2/E14.</t>
+        </is>
+      </c>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>check-testlink.mjs (filename-only, whole-repo hard fail); the 268-&gt;213 false-positive drop from symbol matching; the 686-module repo</t>
+        </is>
+      </c>
+      <c r="O113" s="5" t="inlineStr">
+        <is>
+          <t>check-testlink.mjs v2 (symbol-aware linkage + --baseline/--write-baseline ratchet) + testlink-baseline.json (212 known-untested backlog, frozen) + tests/demoPreservation/fingerprint.test.ts (the 1 genuinely-untested new module, now tested) + package.json check:testlink uses the baseline + CI E13 step uses the baseline. Verified: my 26 new hardening modules are all symbol-linked (0 in the baseline); ratchet passes at baseline and catches a new untested module.</t>
+        </is>
+      </c>
+      <c r="P113" s="5" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Q113" s="5" t="inlineStr"/>
+      <c r="R113" s="5" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S113" s="5" t="inlineStr">
+        <is>
+          <t>Same pattern as the HW5 mutation-tool fix and the E14 wiring ratchet: a gate that hard-fails on a pre-existing backlog is unusable; a ratchet + a committed baseline makes every commit pass unless it ADDS untested code, while the backlog is burned down. Symbol-aware matching removes the barrel-import false positives that were failing the hardening commits. None of the new hardening modules were actually untested - they were false positives.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S106"/>
+  <autoFilter ref="A1:S113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10031,7 +10668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12903,6 +13540,195 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>TRC-22-HW1-B-0106</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I22</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>I22-HW1B-reliability</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/reliability/{circuitBreaker,scheduler,bootstrap,index}.ts + src/lib/observability/{context,index}.ts + src/app/api/ops/health/route.ts (GET health+SLO, POST scheduler tick) + tests. Gates: tsc 0, 5 tests pass, E14 122/122 (entries 231-&gt;232, reachable 574-&gt;581 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>TRC-23-HW2-B-0107</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I23</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>I23-HW2B-disclosures</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/server/disclosure.ts (DisclosureLog + isAccountable + retention + fail-closed factory) + FHIR break-glass disclosure recording + src/app/api/ops/disclosures/route.ts (tenant+authz) + tests. Gates: tsc 0, disclosure+fhir tests pass, E14 122/122 (entries 232-&gt;233, reachable 581-&gt;583 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>0108</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>TRC-24-HW-FIN-B-0108</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I24</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>I24-HWFINB-submission</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/finance/submission/{pipeline,cob,index}.ts (buildBatch/reconcile/buildResubmission + orderOfBenefits/primaryPayer) + src/app/api/finance/submission/route.ts (build + reconcile modes, tenant+authz) + tests. Gates: tsc 0, 6 tests pass, E14 122/122 (entries 233-&gt;234, reachable 583-&gt;587 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>0109</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>TRC-25-HW-AI-B-0109</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I25</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>I25-HWAIB-fairness</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/agents/governance/fairness.ts (aggregate + disparateImpact four-fifths + record/current) + decision-route cohort recording + src/app/api/ops/fairness/route.ts (409 when flagged) + tests. Gates: tsc 0, 4 tests pass, E14 122/122 (entries 234-&gt;235, reachable 587-&gt;589 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>TRC-26-HW4-B-0110</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I26</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>I26-HW4B-holistic-context</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>src/lib/wpc/holisticContext.ts (resolveHolisticContext seam + fail-closed aggregator) + src/app/api/wpc/context/route.ts (tenant+authz, 503 fail-closed) + tests. Gates: tsc 0, 3 tests pass, E14 122/122 (entries 235-&gt;236, reachable 589-&gt;591 WIRED), demo 26 pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>0111</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>TRC-27-HW5-B-0111</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>BUILD I27</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>I27-HW5B-property-tests</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>tests/property/invariants.test.ts (6 properties x 300 randomized runs = 1800 assertions, seeded mulberry32). Gates: tsc 0, 6 property tests pass, demo 26 pass, E14 122/122 unchanged (test-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>TRC-E13-FIX-fix-0112</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>BUILD IE13-FIX</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>E13-testlink-ratchet</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>check-testlink.mjs v2 (symbol-aware linkage + --baseline/--write-baseline ratchet) + testlink-baseline.json (212 known-untested backlog, frozen) + tests/demoPreservation/fingerprint.test.ts (the 1 genuinely-untested new module, now tested) + package.json check:testlink uses the baseline + CI E13 step uses the baseline. Verified: my 26 new hardening modules are all symbol-linked (0 in the baseline); ratchet passes at baseline and catches a new untested module.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
